--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -1,155 +1,139 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079EA92B-5BFC-491C-85FC-F56C5ED76330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3440" yWindow="6450" windowWidth="40520" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="通用表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>##var</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>DeftualNumber</t>
+  </si>
+  <si>
+    <t>NumberLimit</t>
   </si>
   <si>
     <t>##type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropertyType</t>
+  </si>
+  <si>
+    <t>TbLocalzationKeyData#sep=+</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <t>##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remark</t>
+  </si>
+  <si>
+    <t>属性</t>
   </si>
   <si>
     <t>名字多语言</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DeftualNumber</t>
-  </si>
-  <si>
-    <t>NumberLimit</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>默认值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>最大值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbLocalzationKeyData#sep=+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PropertyType</t>
-  </si>
-  <si>
-    <t>Property</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>金币</t>
   </si>
   <si>
+    <t>UIText+Gold</t>
+  </si>
+  <si>
+    <t>通用游戏货币</t>
+  </si>
+  <si>
     <t>游戏币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIText+GameGold</t>
+  </si>
+  <si>
+    <t>游戏玩法货币</t>
   </si>
   <si>
     <t>体力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIText+Strength</t>
+  </si>
+  <si>
+    <t>体力值</t>
   </si>
   <si>
     <t>行动值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用游戏货币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏玩法货币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体力值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UIText+Gold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UIText+GameGold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UIText+Strength</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>UIText+ActionPointsValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本生产量</t>
+  </si>
+  <si>
+    <t>基础良品率</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -157,12 +141,175 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -175,8 +322,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -184,39 +517,350 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -265,7 +909,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -300,7 +944,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -474,96 +1118,92 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="37.75" customWidth="1"/>
-    <col min="4" max="4" width="17.9140625" customWidth="1"/>
-    <col min="5" max="5" width="17.58203125" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="8.66666666666667" style="1"/>
+    <col min="2" max="2" width="11.3333333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.9166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.5833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.3333333333333" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>15</v>
+    <row r="4" spans="1:11">
+      <c r="B4" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="1">
@@ -573,15 +1213,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>16</v>
+    <row r="5" spans="1:11">
+      <c r="B5" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E5" s="1">
         <v>10</v>
@@ -590,15 +1230,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>17</v>
+    <row r="6" spans="1:11">
+      <c r="B6" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E6" s="1">
         <v>100</v>
@@ -607,15 +1247,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>18</v>
+    <row r="7" spans="1:11">
+      <c r="B7" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>18</v>
+      <c r="D7" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -624,15 +1264,40 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+    <row r="8" spans="1:11">
+      <c r="B8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="8">
+        <v>50</v>
+      </c>
       <c r="F8" s="1"/>
     </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="K12" s="9"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDFD4A6-AFBC-4284-8D13-D76794047AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E5A721-F8B6-48FA-9F29-FF43F5AFEC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7580" yWindow="4380" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -117,13 +117,32 @@
   </si>
   <si>
     <t>UIText+ActionPointsValue</t>
+  </si>
+  <si>
+    <t>爱心币</t>
+  </si>
+  <si>
+    <t>UIText+HeartCoins</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱心币</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIText+ClawMachineValue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>娃娃机游戏次数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +165,14 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -175,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -193,6 +220,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -474,7 +507,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.75" customWidth="1"/>
     <col min="3" max="3" width="37.75" customWidth="1"/>
     <col min="4" max="4" width="17.9140625" customWidth="1"/>
     <col min="5" max="5" width="17.58203125" customWidth="1"/>
@@ -609,6 +642,40 @@
         <v>5</v>
       </c>
     </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>15</v>
+      </c>
+    </row>
     <row r="10" spans="1:11" ht="14.5" x14ac:dyDescent="0.3">
       <c r="K10" s="6"/>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E5A721-F8B6-48FA-9F29-FF43F5AFEC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3231D3E-7D67-4EBD-BA23-C5D22A59A08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,7 +585,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="1">
-        <v>100</v>
+        <v>999999</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E5A721-F8B6-48FA-9F29-FF43F5AFEC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -123,26 +117,25 @@
   </si>
   <si>
     <t>UIText+HeartCoins</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱心币</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>娃娃机游戏次数</t>
   </si>
   <si>
     <t>UIText+ClawMachineValue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>娃娃机游戏次数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,29 +147,161 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="黑体"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,8 +314,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -198,9 +509,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -213,8 +766,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -222,24 +781,62 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -497,24 +1094,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.66666666666667" style="1"/>
     <col min="2" max="2" width="18.75" customWidth="1"/>
     <col min="3" max="3" width="37.75" customWidth="1"/>
-    <col min="4" max="4" width="17.9140625" customWidth="1"/>
-    <col min="5" max="5" width="17.58203125" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.9166666666667" customWidth="1"/>
+    <col min="5" max="5" width="17.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="22.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +1131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -554,7 +1151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -574,7 +1171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
@@ -585,13 +1182,13 @@
         <v>19</v>
       </c>
       <c r="E4" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="B5" s="5" t="s">
         <v>20</v>
       </c>
@@ -602,13 +1199,13 @@
         <v>22</v>
       </c>
       <c r="E5" s="1">
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="F5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
@@ -625,7 +1222,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
@@ -642,32 +1239,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="F8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="B9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -676,11 +1273,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="K10" s="6"/>
+    <row r="10" spans="1:11">
+      <c r="K10" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24496C0A-83C2-4152-A15A-D8FE5C9927A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC2CE9F-9970-4F27-B2C0-9AC2DB438F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="1980" windowWidth="30580" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7970" yWindow="4630" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,18 @@
   </si>
   <si>
     <t>金币</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉丝数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>女主(粉丝数量)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnumsText+Fen</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -204,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -231,6 +243,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -682,6 +697,21 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+      <c r="F10" s="1">
+        <v>-1</v>
+      </c>
       <c r="K10" s="7"/>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC2CE9F-9970-4F27-B2C0-9AC2DB438F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5802E6A3-EDC7-4356-9D50-169A1990B713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7970" yWindow="4630" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10370" yWindow="4760" windowWidth="30580" windowHeight="17170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -141,6 +141,16 @@
   </si>
   <si>
     <t>EnumsText+Fen</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉丝增长系数</t>
+  </si>
+  <si>
+    <t>EnumsText+Fen</t>
+  </si>
+  <si>
+    <t>粉丝增长系数(百分比)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -523,13 +533,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
     <col min="2" max="2" width="18.75" customWidth="1"/>
     <col min="3" max="3" width="37.75" customWidth="1"/>
-    <col min="4" max="4" width="17.9140625" customWidth="1"/>
+    <col min="4" max="4" width="24.58203125" customWidth="1"/>
     <col min="5" max="5" width="17.58203125" customWidth="1"/>
     <col min="6" max="6" width="22.33203125" customWidth="1"/>
   </cols>
@@ -714,6 +724,23 @@
       </c>
       <c r="K10" s="7"/>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="1">
+        <v>100</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5802E6A3-EDC7-4356-9D50-169A1990B713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F9BF1E-EA38-491C-9EC0-49077BA560C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10370" yWindow="4760" windowWidth="30580" windowHeight="17170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59220" yWindow="6375" windowWidth="30585" windowHeight="18375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>最大值</t>
   </si>
   <si>
-    <t>UIText+Gold</t>
-  </si>
-  <si>
     <t>通用游戏货币</t>
   </si>
   <si>
@@ -151,6 +148,10 @@
   </si>
   <si>
     <t>粉丝增长系数(百分比)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnumsText+Coin</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -606,13 +607,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E4" s="1">
         <v>10000</v>
@@ -623,13 +624,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E5" s="1">
         <v>10000</v>
@@ -640,13 +641,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="E6" s="1">
         <v>100</v>
@@ -657,13 +658,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -674,13 +675,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1">
         <v>10000</v>
@@ -691,13 +692,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="D9" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -708,13 +709,13 @@
     </row>
     <row r="10" spans="1:11" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="E10" s="1">
         <v>100</v>
@@ -726,13 +727,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="E11" s="1">
         <v>100</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F9BF1E-EA38-491C-9EC0-49077BA560C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B2A630-EBA5-4EE2-8E85-B28FAE0715EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59220" yWindow="6375" windowWidth="30585" windowHeight="18375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4590" yWindow="4120" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -152,6 +152,14 @@
   </si>
   <si>
     <t>EnumsText+Coin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>人气数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnumsText+Popularity</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -534,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
@@ -742,6 +750,23 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B2A630-EBA5-4EE2-8E85-B28FAE0715EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446DA0D4-966D-418A-B421-33502944715E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4590" yWindow="4120" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12570" yWindow="5540" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -155,11 +155,14 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>人气数</t>
+    <t>曝光值</t>
+  </si>
+  <si>
+    <t>EnumsText+ExposureValue</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EnumsText+Popularity</t>
+    <t>曝光值</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -758,7 +761,7 @@
         <v>39</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446DA0D4-966D-418A-B421-33502944715E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BDB936-E4EF-429D-BEB6-F9C0E36B9684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12570" yWindow="5540" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5560" yWindow="2440" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用表" sheetId="1" r:id="rId1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PropertyData.xlsx
@@ -1,29 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CB9750-493A-4491-9F92-2C63BFF38981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30590" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="通用表" sheetId="1" r:id="rId4"/>
+    <sheet name="通用表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1784603129" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1784603129" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1784603129" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1784603129"/>
+      <pm:revision xmlns:pm="smNativeData" day="1784705213" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784705213" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784705213" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784705213"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -112,13 +117,13 @@
     <t>钓鱼等级</t>
   </si>
   <si>
-    <t>UIText+FishLevel</t>
+    <t>Fish+Fish/Level</t>
   </si>
   <si>
     <t>钓鱼经验</t>
   </si>
   <si>
-    <t>UIText+FishExp</t>
+    <t>Fish+Fish/Experience</t>
   </si>
   <si>
     <t>爱心币</t>
@@ -158,71 +163,91 @@
   </si>
   <si>
     <t>曝光值</t>
+  </si>
+  <si>
+    <t>MachiRoom+MachiInspire</t>
+  </si>
+  <si>
+    <t>马吉灵感值</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>MachiRoom+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>MachiPressure</t>
+    </r>
+  </si>
+  <si>
+    <t>马吉压力值</t>
+  </si>
+  <si>
+    <t>MachiInspire</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MachiPressure</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784603129" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784603129" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="黑体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <name val="黑体"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1784603129" ulstyle="none" kern="1">
-            <pm:latin face="黑体" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -233,160 +258,91 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784603129" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA8D08C"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784603129" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1784603129" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784603129"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784603129"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784603129"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1784603129"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1784603129" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784705213" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1784603129" count="3">
+      <pm:colors xmlns:pm="smNativeData" id="1784705213" count="4">
         <pm:color name="颜色 24" rgb="70AD47"/>
         <pm:color name="20% 灰色" rgb="000000"/>
         <pm:color name="颜色 26" rgb="A8D08C"/>
+        <pm:color name="黑色" rgb="000000"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -648,19 +604,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.663793" customWidth="1" style="1"/>
-    <col min="2" max="2" width="18.750000" customWidth="1"/>
-    <col min="3" max="3" width="37.750000" customWidth="1"/>
-    <col min="4" max="4" width="24.577586" customWidth="1"/>
-    <col min="5" max="5" width="17.577586" customWidth="1"/>
-    <col min="6" max="6" width="22.327586" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.75" customWidth="1"/>
+    <col min="3" max="3" width="37.75" customWidth="1"/>
+    <col min="4" max="4" width="24.58203125" customWidth="1"/>
+    <col min="5" max="5" width="17.58203125" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -680,7 +636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -700,7 +656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -720,24 +676,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="1">
         <v>10000</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
@@ -747,14 +703,14 @@
       <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="1">
         <v>10000</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
@@ -764,14 +720,14 @@
       <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="1">
         <v>100</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
@@ -781,156 +737,174 @@
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="1">
         <v>5</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="8" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="1">
         <v>10000</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="1:11" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="1">
         <v>100</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="1">
         <v>-1</v>
       </c>
-      <c r="K12" s="7"/>
-    </row>
-    <row r="13" spans="2:6">
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="1">
         <v>100</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="6" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="1">
         <v>-1</v>
       </c>
     </row>
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1784603129" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1784603129" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1784603129" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784603129" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1784603129" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784603129" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784705213" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
